--- a/pricing-data.xlsx
+++ b/pricing-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Madhu\Coding\PO 2026\pitch-builder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D847EE5C-2563-427E-AB8C-82ED40F67356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDE8F57-CBF1-4D6D-8014-B3D539B0A291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -670,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="3">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>10</v>
@@ -730,7 +730,7 @@
         <v>17</v>
       </c>
       <c r="E5" s="3">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>18</v>

--- a/pricing-data.xlsx
+++ b/pricing-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Madhu\Coding\PO 2026\pitch-builder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDE8F57-CBF1-4D6D-8014-B3D539B0A291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA66F649-391E-4293-B3CF-BA20D4F9497C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,18 +125,12 @@
     <t>Stage Branding</t>
   </si>
   <si>
-    <t>Your logo on the main stage backdrop, visible in every photo, video, and livestream across all 3 nights (Sep 4–6).</t>
-  </si>
-  <si>
     <t>mc-mentions</t>
   </si>
   <si>
     <t>MC Mentions / Announcements</t>
   </si>
   <si>
-    <t>Live on-mic shoutouts from the event MC throughout the 3-day celebration.</t>
-  </si>
-  <si>
     <t>naming-rights</t>
   </si>
   <si>
@@ -218,18 +212,9 @@
     <t>Onam Sadya Sponsorship</t>
   </si>
   <si>
-    <t>Sponsor the Grand Onam Sadya — Onam's most cherished tradition, with 2,000+ participants.</t>
-  </si>
-  <si>
     <t>cultural-program</t>
   </si>
   <si>
-    <t>Cultural Program Sponsorship</t>
-  </si>
-  <si>
-    <t>Brand association with traditional cultural performances and heritage programs.</t>
-  </si>
-  <si>
     <t>key</t>
   </si>
   <si>
@@ -258,6 +243,21 @@
   </si>
   <si>
     <t>Permanent logo placement on the official Ponn Onam 2026 posters and flyers</t>
+  </si>
+  <si>
+    <t>Live on-mic shoutouts from the event MC throughout the 2-day celebration.</t>
+  </si>
+  <si>
+    <t>Your logo on the main stage backdrop, visible in every photo, video, and livestream across all 2 nights (Sep 4–6).</t>
+  </si>
+  <si>
+    <t>Sponsor the Grand Onam Sadya — Onam's most cherished tradition, with 2,000+ participants.Custom gifts can be given</t>
+  </si>
+  <si>
+    <t>Concert event Sponsorship</t>
+  </si>
+  <si>
+    <t>Brand association with the concert</t>
   </si>
 </sst>
 </file>
@@ -670,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="3">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>10</v>
@@ -690,7 +690,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="3">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -713,7 +713,7 @@
         <v>8000</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -730,7 +730,7 @@
         <v>17</v>
       </c>
       <c r="E5" s="3">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>18</v>
@@ -813,7 +813,7 @@
         <v>100000</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -824,16 +824,16 @@
         <v>31</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E10" s="3">
         <v>20000</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -844,16 +844,16 @@
         <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E11" s="3">
         <v>300000</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -864,156 +864,156 @@
         <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E12" s="3">
         <v>35000</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="3">
-        <v>90000</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="3">
-        <v>120000</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="3">
-        <v>30000</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="3">
+        <v>30000</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="3">
-        <v>50000</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E17" s="3">
         <v>25000</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="3">
-        <v>150000</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E19" s="3">
         <v>80000</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1032,7 +1032,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -1040,34 +1040,34 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/pricing-data.xlsx
+++ b/pricing-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Madhu\Coding\PO 2026\pitch-builder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA66F649-391E-4293-B3CF-BA20D4F9497C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2C9892-43BF-4D3D-920E-4A4B378573B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="82">
   <si>
     <t>category</t>
   </si>
@@ -258,6 +258,15 @@
   </si>
   <si>
     <t>Brand association with the concert</t>
+  </si>
+  <si>
+    <t>stall-main</t>
+  </si>
+  <si>
+    <t>Stall Space</t>
+  </si>
+  <si>
+    <t>A premium stall at the Main event on Sep 4,5, face-to-face with qualified, high-intent residential buyers.</t>
   </si>
 </sst>
 </file>
@@ -625,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -824,16 +833,16 @@
         <v>31</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="E10" s="3">
-        <v>20000</v>
+        <v>75000</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -844,16 +853,16 @@
         <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E11" s="3">
-        <v>300000</v>
+        <v>20000</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -864,36 +873,36 @@
         <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E12" s="3">
-        <v>35000</v>
+        <v>300000</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E13" s="3">
-        <v>20000</v>
+        <v>35000</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -904,16 +913,16 @@
         <v>43</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E14" s="3">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -924,16 +933,16 @@
         <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E15" s="3">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -944,36 +953,36 @@
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E16" s="3">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E17" s="3">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
@@ -984,19 +993,19 @@
         <v>57</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E18" s="3">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>56</v>
       </c>
@@ -1004,15 +1013,35 @@
         <v>57</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E20" s="3">
         <v>80000</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>78</v>
       </c>
     </row>
